--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -7738,7 +7738,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -7738,7 +7738,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>plus</t>
+          <t>transdermal</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>topspot</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>spoton</t>
         </is>
       </c>
     </row>

--- a/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
+++ b/Tratamento/src/Dados_limpos/novos/limpo_petz_20260201_201629.xlsx
@@ -5044,7 +5044,7 @@
       </c>
       <c r="P62" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5278,7 +5278,7 @@
       </c>
       <c r="P65" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5434,7 +5434,7 @@
       </c>
       <c r="P67" t="inlineStr">
         <is>
-          <t>transdermal</t>
+          <t>plus</t>
         </is>
       </c>
     </row>
@@ -5660,7 +5660,7 @@
       </c>
       <c r="P70" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -5800,7 +5800,7 @@
       </c>
       <c r="P72" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6182,7 +6182,7 @@
       </c>
       <c r="P77" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -6338,7 +6338,7 @@
       </c>
       <c r="P79" t="inlineStr">
         <is>
-          <t>spot</t>
+          <t>topspot</t>
         </is>
       </c>
     </row>
@@ -7738,7 +7738,7 @@
       </c>
       <c r="P98" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7814,7 +7814,7 @@
       </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
@@ -7890,7 +7890,7 @@
       </c>
       <c r="P100" t="inlineStr">
         <is>
-          <t>spoton</t>
+          <t>spot</t>
         </is>
       </c>
     </row>
